--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>36.9</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="16">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>890191</v>
+        <v>890704</v>
       </c>
     </row>
     <row r="17"/>

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>890704</v>
+        <v>890711</v>
       </c>
     </row>
     <row r="17"/>

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.002500000000000001</v>
+        <v>0.002588441050000003</v>
       </c>
     </row>
     <row r="9">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.002500000000000001</v>
+        <v>0.002411990949999999</v>
       </c>
     </row>
     <row r="10"/>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>66.54000000000001</v>
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>36.91</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="16">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>890711</v>
+        <v>904755</v>
       </c>
     </row>
     <row r="17"/>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>27</v>
+        <v>26.945617</v>
       </c>
     </row>
     <row r="24">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>50</v>
+        <v>50.5031831</v>
       </c>
     </row>
     <row r="25">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>32</v>
+        <v>31.7695989</v>
       </c>
     </row>
     <row r="26">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>55</v>
+        <v>55.68006520000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>fli_fars_2026-08-28.tif</t>
+          <t>fli_fars_2026-08-29.tif</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>64.48999999999999</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="15">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>36.36</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="16">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -7,9 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="گزارش FIRIS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="خلاصه" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="مناطق_چهارگانه" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="مناطق_شکار_ممنوع" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="طبقات_خطر" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="اطلاعات_فنی" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'مناطق_چهارگانه'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'مناطق_شکار_ممنوع'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'طبقات_خطر'!$A$1:$E$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,20 +34,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="B Nazanin"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
+      <name val="B Nazanin"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDD835"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FB8C00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E53935"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00880E4F"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -51,25 +102,48 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00C9CED3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9CED3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9CED3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9CED3"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,224 +508,1708 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>گزارش سامانه FIRIS استان فارس</t>
+          <t>گزارش خطر حریق استان فارس</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>تاریخ اجرا</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>تاریخ پیش‌بینی</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>فایل ورودی</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>فایل FLI</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>fli_fars_2026-08-29.tif</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>سیستم مختصات</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>EPSG:4326</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>عرض Raster</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2000</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>تعداد سلول معتبر</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>904755</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>ارتفاع Raster</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>2000</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>اندازه سلول X</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>67.27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>میانگین FLI</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>36.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>طبقه خطر استان</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>رزولوشن X</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>0.002588441050000003</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>اندازه سلول Y</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>رزولوشن Y</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
         <v>0.002411990949999999</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>آمار شاخص FLI</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>حداقل FLI</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>حداکثر FLI</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>67.27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>میانگین FLI</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>36.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>تعداد سلول معتبر</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>904755</v>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>طبقه‌بندی خطر</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>طبقه خطر بر اساس میانگین</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>محدوده مکانی</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>جنوب</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>26.945617</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>غرب</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>50.5031831</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>شمال</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>31.7695989</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>شرق</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>55.68006520000001</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>نام منطقه</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>نوع منطقه</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>میانگین FLI</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>تعداد سلول معتبر</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>طبقه خطر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه خرسي</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>24441</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع پادنا</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>43.22</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>5703</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع دره باغ</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>751</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه دراء</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>10563</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع خرمنکوه</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1663</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع مل بلند</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>51.72</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>2137</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع دالان</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>52.77</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع توت سياه</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع مهارلو</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>43.22</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1059</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع روشن کوه</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>3976</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه گورم</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>5465</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوهستان</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>6849</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع چاه نفت</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع مزايجان</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>932</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه سياه</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>4808</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه هوا و</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>4944</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع بصيران</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>5180</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع بناب</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>3925</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممن.ع آق جلو</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>657</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه خم</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>6257</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع شیکوه</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>کم</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>نام منطقه</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>نوع منطقه</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>میانگین FLI</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>تعداد سلول معتبر</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>طبقه خطر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده تنگ بستانک</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>2293</v>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده میانجنگل فسا</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>4823</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده هرمود</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>868</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده مارگون</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>466</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده بهرام گور</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>پارک ملي قطرويه</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده ارژن و پريشان</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>7042</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>پناهگاه حيات وحش دره باغ</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده ماله گاله</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>6931</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>پارک ملی بمو</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>5654</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>پناهگاه حيات وحش بختگان</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>16529</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>پارک ملي بختگان</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>5265</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده برم فیروز</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>2311</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>51.18</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1185</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>طبقه خطر</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>تعداد سلول</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>درصد از کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>کم</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>39470</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>581658</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>64.29000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>283526</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>31.34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>خیلی زیاد</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>بحرانی</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CRS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:4326</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Resolution X</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>0.002588441050000003</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Resolution Y</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.002411990949999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>50.5031831</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>26.945617</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>55.68006520000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>31.7695989</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Transform a</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.002588441050000003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Transform b</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Transform c</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>50.5031831</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Transform d</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Transform e</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>-0.002411990949999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Transform f</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>31.7695989</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -130,10 +130,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-08-29.tif</t>
+          <t>fli_fars_2026-08-30.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>67.27</v>
+        <v>68.22</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>36.05</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="10">
@@ -718,20 +718,20 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39.94</v>
+        <v>40.95</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>27.04</v>
+        <v>27.15</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>57.27</v>
+        <v>56.59</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -750,20 +750,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>43.22</v>
+        <v>39.88</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>31.02</v>
+        <v>28.27</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.99</v>
+        <v>54.67</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -782,18 +782,18 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>36.31</v>
+        <v>31.8</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>57.76</v>
+        <v>50.95</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -814,18 +814,18 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44.79</v>
+        <v>43.05</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>36.39</v>
+        <v>36.34</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>59.05</v>
+        <v>57.6</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -846,18 +846,18 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>35.72</v>
+        <v>36.86</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>28.62</v>
+        <v>30.2</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45.65</v>
+        <v>47.05</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -878,18 +878,18 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>39.03</v>
+        <v>38.8</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>31.75</v>
+        <v>31.36</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>51.72</v>
+        <v>49.86</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -910,18 +910,18 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>33.27</v>
+        <v>35.39</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>52.77</v>
+        <v>56.1</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -942,18 +942,18 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>42.35</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>34.53</v>
+        <v>34.02</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>55.16</v>
+        <v>54.93</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -974,18 +974,18 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>32.41</v>
+        <v>32.42</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>26.11</v>
+        <v>26.58</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>43.22</v>
+        <v>43.36</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1006,20 +1006,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>37.52</v>
+        <v>41.96</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>27.41</v>
+        <v>33.62</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>53.48</v>
+        <v>58.61</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1038,20 +1038,20 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>40.89</v>
+        <v>39.27</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>28.06</v>
+        <v>28.68</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>60.02</v>
+        <v>55.62</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1070,18 +1070,18 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>43.04</v>
+        <v>47.44</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>32.14</v>
+        <v>37.19</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>56.83</v>
+        <v>62.74</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1102,18 +1102,18 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>23.65</v>
+        <v>23.02</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>33.83</v>
+        <v>31.04</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1134,18 +1134,18 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>26.42</v>
+        <v>31.58</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>48.18</v>
+        <v>56.1</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1166,18 +1166,18 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>38.41</v>
+        <v>38.62</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>26.32</v>
+        <v>29.42</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>55.41</v>
+        <v>53.07</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1198,18 +1198,18 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>26.45</v>
+        <v>27.63</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.12</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>48.26</v>
+        <v>50.17</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>41.14</v>
+        <v>39.97</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>58.36</v>
+        <v>57.44</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1262,18 +1262,18 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>33.63</v>
+        <v>35.22</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>49.07</v>
+        <v>51.83</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1294,20 +1294,20 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>37.82</v>
+        <v>40.27</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>28.59</v>
+        <v>31.62</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>48.86</v>
+        <v>50.44</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1326,20 +1326,20 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>42.86</v>
+        <v>39.14</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>27.36</v>
+        <v>28.11</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>59.22</v>
+        <v>55.05</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>18.67</v>
+        <v>19.53</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>43.37</v>
+        <v>46.38</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,20 +1458,20 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>41.36</v>
+        <v>39.84</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>33.21</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>52.56</v>
+        <v>51.95</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1490,18 +1490,18 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>38.11</v>
+        <v>38.33</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>28.91</v>
+        <v>30.02</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>55.21</v>
+        <v>54.11</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1522,18 +1522,18 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>24.32</v>
+        <v>23.85</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45.37</v>
+        <v>44.26</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1554,18 +1554,18 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>39.59</v>
+        <v>37.83</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>31.35</v>
+        <v>29.62</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>51.01</v>
+        <v>49.3</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1586,18 +1586,18 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>26.07</v>
+        <v>30.82</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>51.04</v>
+        <v>60.87</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1618,18 +1618,18 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>32.67</v>
+        <v>38.73</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>4.57</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>40.41</v>
+        <v>47.15</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1650,18 +1650,18 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>41.91</v>
+        <v>43.79</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>29.93</v>
+        <v>31.77</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>60.3</v>
+        <v>62.81</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1682,18 +1682,18 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>28.71</v>
+        <v>25.41</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>57.76</v>
+        <v>50.95</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1714,20 +1714,20 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>41.07</v>
+        <v>38.62</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>29.49</v>
+        <v>28.09</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>60.27</v>
+        <v>59.72</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1746,18 +1746,18 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>36.33</v>
+        <v>36.91</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>27.7</v>
+        <v>27.32</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>50.21</v>
+        <v>51.35</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1778,18 +1778,18 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>35.62</v>
+        <v>37.59</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.21</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>53.7</v>
+        <v>54.74</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1810,18 +1810,18 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>34.25</v>
+        <v>36.66</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>3.25</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>50.27</v>
+        <v>53.22</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1842,18 +1842,18 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>39.88</v>
+        <v>38.6</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>29.95</v>
+        <v>28.84</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>52.47</v>
+        <v>51.44</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1874,20 +1874,20 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>38.97</v>
+        <v>40.04</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>32.67</v>
+        <v>32.13</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>51.18</v>
+        <v>51.74</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1954,14 +1954,14 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39470</v>
+        <v>39698</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1973,14 +1973,14 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>581658</v>
+        <v>570637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>64.29000000000001</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>283526</v>
+        <v>294132</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>31.34</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-08-30.tif</t>
+          <t>fli_fars_2026-08-31.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>68.22</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>36.28</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="10">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>40.95</v>
+        <v>40.14</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>27.15</v>
+        <v>26.93</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.59</v>
+        <v>56.22</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,20 +750,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>39.88</v>
+        <v>40.85</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>28.27</v>
+        <v>28.04</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>54.67</v>
+        <v>54.98</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>31.8</v>
+        <v>31.73</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>50.95</v>
+        <v>51.64</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>43.05</v>
+        <v>47.62</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>36.34</v>
+        <v>40.03</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>57.6</v>
+        <v>58.9</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>36.86</v>
+        <v>37.86</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>30.2</v>
+        <v>30.41</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>47.05</v>
+        <v>48.38</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
@@ -878,20 +878,20 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>38.8</v>
+        <v>40.4</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>31.36</v>
+        <v>32.76</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>49.86</v>
+        <v>52.42</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>35.39</v>
+        <v>33.67</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.1</v>
+        <v>52.66</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>41</v>
+        <v>41.96</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>34.02</v>
+        <v>32.57</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>54.93</v>
+        <v>54.72</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>32.42</v>
+        <v>32.47</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>26.58</v>
+        <v>25.61</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>43.36</v>
+        <v>42.95</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
@@ -1006,20 +1006,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>41.96</v>
+        <v>37.59</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>33.62</v>
+        <v>29.48</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>58.61</v>
+        <v>52.31</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>39.27</v>
+        <v>39.85</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>28.68</v>
+        <v>29.02</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>55.62</v>
+        <v>54.95</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>47.44</v>
+        <v>46.26</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>37.19</v>
+        <v>36.09</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>62.74</v>
+        <v>61.03</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>23.02</v>
+        <v>23.14</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>31.04</v>
+        <v>31.41</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>31.58</v>
+        <v>30.75</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>56.1</v>
+        <v>54.28</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>38.62</v>
+        <v>38.84</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>29.42</v>
+        <v>28.41</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>53.07</v>
+        <v>53.39</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>27.63</v>
+        <v>26.13</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.12</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>50.17</v>
+        <v>47.91</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>39.97</v>
+        <v>40.25</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>57.44</v>
+        <v>54.23</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>35.22</v>
+        <v>32.69</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>51.83</v>
+        <v>48.4</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>40.27</v>
+        <v>40.77</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>31.62</v>
+        <v>32.75</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>50.44</v>
+        <v>51.56</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>39.14</v>
+        <v>38.26</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>28.11</v>
+        <v>28.61</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>55.05</v>
+        <v>51.57</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>19.53</v>
+        <v>18.04</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>46.38</v>
+        <v>40.08</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39.84</v>
+        <v>38.82</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>31</v>
+        <v>29.67</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>51.95</v>
+        <v>51.15</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
@@ -1490,20 +1490,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>38.33</v>
+        <v>40.63</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>30.02</v>
+        <v>32.67</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>54.11</v>
+        <v>56.19</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>23.85</v>
+        <v>24.14</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44.26</v>
+        <v>45.46</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>37.83</v>
+        <v>37.29</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>29.62</v>
+        <v>29.04</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>49.3</v>
+        <v>48.94</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>30.82</v>
+        <v>28.91</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>60.87</v>
+        <v>56.73</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>38.73</v>
+        <v>36.32</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>4.57</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>47.15</v>
+        <v>44.44</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>43.79</v>
+        <v>41.99</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>31.77</v>
+        <v>31.75</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>62.81</v>
+        <v>58.45</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>25.41</v>
+        <v>25.72</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>50.95</v>
+        <v>51.64</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
@@ -1714,20 +1714,20 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>38.62</v>
+        <v>40.07</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>28.09</v>
+        <v>29.49</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>59.72</v>
+        <v>58.97</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>36.91</v>
+        <v>36.6</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>27.32</v>
+        <v>26.46</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>51.35</v>
+        <v>51.45</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
@@ -1784,7 +1784,7 @@
         <v>3.21</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>54.74</v>
+        <v>56.37</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>36.66</v>
+        <v>37.46</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>3.25</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>53.22</v>
+        <v>54.93</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>38.6</v>
+        <v>38.9</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>28.84</v>
+        <v>30.71</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>51.44</v>
+        <v>49.24</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
@@ -1874,20 +1874,20 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>40.04</v>
+        <v>37.1</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>32.13</v>
+        <v>29.82</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>51.74</v>
+        <v>49.68</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1954,10 +1954,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39698</v>
+        <v>39658</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="3">
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>570637</v>
+        <v>547652</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>63.07</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>294132</v>
+        <v>317029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>32.51</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>288</v>
+        <v>416</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="خلاصه" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="مناطق_چهارگانه" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مناطق_شکار_ممنوع" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مناطق_شکار_ممنوع" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="مناطق چهارگانه" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="طبقات_خطر" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="اطلاعات_فنی" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'مناطق_چهارگانه'!$A$1:$H$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'مناطق_شکار_ممنوع'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'مناطق_شکار_ممنوع'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'مناطق چهارگانه'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'طبقات_خطر'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -653,7 +653,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
@@ -810,7 +810,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
@@ -970,7 +970,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق_شکار_ممنوع</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
@@ -1393,7 +1393,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="خلاصه" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="مناطق_شکار_ممنوع" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مناطق چهارگانه" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مناطق_چهارگانه" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="مناطق_شکار_ممنوع" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="طبقات_خطر" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="اطلاعات_فنی" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'مناطق_شکار_ممنوع'!$A$1:$H$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'مناطق چهارگانه'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'مناطق_چهارگانه'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'مناطق_شکار_ممنوع'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'طبقات_خطر'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -653,7 +653,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
@@ -810,7 +810,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
@@ -970,7 +970,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>مناطق_شکار_ممنوع</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
@@ -1393,7 +1393,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-08-31.tif</t>
+          <t>fli_fars_2026-09-01.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>70.03</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>36.75</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="10">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>40.14</v>
+        <v>41.42</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>26.93</v>
+        <v>26.86</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.22</v>
+        <v>56.28</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>40.85</v>
+        <v>42.36</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>28.04</v>
+        <v>31.11</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>54.98</v>
+        <v>57.15</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>31.73</v>
+        <v>27.29</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>51.64</v>
+        <v>45.47</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>47.62</v>
+        <v>53.12</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>40.03</v>
+        <v>46.22</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>58.9</v>
+        <v>65.14</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>37.86</v>
+        <v>35.87</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>30.41</v>
+        <v>28.06</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>48.38</v>
+        <v>45.27</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>40.4</v>
+        <v>43.48</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>32.76</v>
+        <v>32.37</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>52.42</v>
+        <v>55.59</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>33.67</v>
+        <v>42.78</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>52.66</v>
+        <v>64.06</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -942,20 +942,20 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>41.96</v>
+        <v>37.07</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>32.57</v>
+        <v>28.32</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>54.72</v>
+        <v>51.64</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>32.47</v>
+        <v>33.38</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>25.61</v>
+        <v>27.54</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>42.95</v>
+        <v>43.14</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>37.59</v>
+        <v>38.25</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>29.48</v>
+        <v>26.43</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>52.31</v>
+        <v>57.5</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
@@ -1038,20 +1038,20 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>39.85</v>
+        <v>42.89</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>29.02</v>
+        <v>31.81</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>54.95</v>
+        <v>59.11</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46.26</v>
+        <v>43.49</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>36.09</v>
+        <v>30.02</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>61.03</v>
+        <v>57.81</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>23.14</v>
+        <v>23.78</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>31.41</v>
+        <v>33.51</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>30.75</v>
+        <v>26.57</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>54.28</v>
+        <v>47.13</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
@@ -1166,20 +1166,20 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>38.84</v>
+        <v>41.1</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>28.41</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>53.39</v>
+        <v>56.64</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>26.13</v>
+        <v>30.58</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.12</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>47.91</v>
+        <v>53.46</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>40.25</v>
+        <v>35.51</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>54.23</v>
+        <v>52.14</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>32.69</v>
+        <v>34.64</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>48.4</v>
+        <v>49.17</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
@@ -1294,20 +1294,20 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>40.77</v>
+        <v>38.54</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>32.75</v>
+        <v>29.61</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>51.56</v>
+        <v>49.32</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1326,20 +1326,20 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>38.26</v>
+        <v>43.03</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>28.61</v>
+        <v>29.38</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>51.57</v>
+        <v>58.36</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>18.04</v>
+        <v>17.1</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>40.08</v>
+        <v>38.11</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,20 +1458,20 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>38.82</v>
+        <v>43.2</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>29.67</v>
+        <v>30.53</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>51.15</v>
+        <v>56.56</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1490,20 +1490,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>40.63</v>
+        <v>39.88</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>32.67</v>
+        <v>31.7</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.19</v>
+        <v>56.54</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>24.14</v>
+        <v>24.95</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45.46</v>
+        <v>46.94</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
@@ -1554,20 +1554,20 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>37.29</v>
+        <v>49.61</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>29.04</v>
+        <v>43.25</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>48.94</v>
+        <v>60.66</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>28.91</v>
+        <v>24.79</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>56.73</v>
+        <v>49.23</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>36.32</v>
+        <v>30.4</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>4.57</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44.44</v>
+        <v>37.86</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>41.99</v>
+        <v>48.35</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>31.75</v>
+        <v>38.34</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>58.45</v>
+        <v>67.72</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>25.72</v>
+        <v>22.72</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>51.64</v>
+        <v>45.47</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>40.07</v>
+        <v>46.48</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>29.49</v>
+        <v>35.11</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>58.97</v>
+        <v>60.99</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>36.6</v>
+        <v>36.09</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>26.46</v>
+        <v>27.55</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>51.45</v>
+        <v>50.51</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>37.59</v>
+        <v>34.94</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.21</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>56.37</v>
+        <v>53.11</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>37.46</v>
+        <v>34.12</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>3.25</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>54.93</v>
+        <v>49.24</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
@@ -1842,20 +1842,20 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>38.9</v>
+        <v>46.63</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>30.71</v>
+        <v>35.12</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>49.24</v>
+        <v>58.81</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1874,20 +1874,20 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>37.1</v>
+        <v>43.41</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>29.82</v>
+        <v>35.31</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>49.68</v>
+        <v>58.63</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1954,10 +1954,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39658</v>
+        <v>39149</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="3">
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>547652</v>
+        <v>403123</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>60.53</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>317029</v>
+        <v>458449</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>35.04</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>416</v>
+        <v>4034</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDD835"/>
+        <fgColor rgb="00FB8C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB8C00"/>
+        <fgColor rgb="00FDD835"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,13 +127,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-09-01.tif</t>
+          <t>fli_fars_2026-09-03.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>70.03</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>39.6</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>41.42</v>
+        <v>46.63</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>26.86</v>
+        <v>35.16</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.28</v>
+        <v>61.55</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>42.36</v>
+        <v>44.07</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>31.11</v>
+        <v>30.99</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.15</v>
+        <v>58.79</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>27.29</v>
+        <v>37.84</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45.47</v>
+        <v>56.89</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>53.12</v>
+        <v>42.28</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46.22</v>
+        <v>36.29</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>65.14</v>
+        <v>55.98</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,20 +846,20 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>35.87</v>
+        <v>42.43</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>28.06</v>
+        <v>35.43</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45.27</v>
+        <v>50.83</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>43.48</v>
+        <v>54.24</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>32.37</v>
+        <v>46.36</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>55.59</v>
+        <v>66.94</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>42.78</v>
+        <v>32.22</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>64.06</v>
+        <v>53.7</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -942,20 +942,20 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>37.07</v>
+        <v>45.39</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>28.32</v>
+        <v>35.27</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>51.64</v>
+        <v>58.07</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -974,20 +974,20 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>33.38</v>
+        <v>41.88</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>27.54</v>
+        <v>32.44</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>43.14</v>
+        <v>53.46</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1006,20 +1006,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>38.25</v>
+        <v>42.09</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>26.43</v>
+        <v>33.05</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>57.5</v>
+        <v>59.65</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>42.89</v>
+        <v>42.47</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>31.81</v>
+        <v>33.16</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>59.11</v>
+        <v>57.52</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
@@ -1070,20 +1070,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>43.49</v>
+        <v>39.82</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>30.02</v>
+        <v>27.95</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>57.81</v>
+        <v>54.2</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>23.78</v>
+        <v>22.68</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>33.51</v>
+        <v>31.86</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>26.57</v>
+        <v>26.91</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>47.13</v>
+        <v>47.41</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>41.1</v>
+        <v>45.34</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>28.41</v>
+        <v>36.51</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>56.64</v>
+        <v>62.66</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>30.58</v>
+        <v>27.1</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.12</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>53.46</v>
+        <v>49.6</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>35.51</v>
+        <v>46.01</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>52.14</v>
+        <v>62.8</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>34.64</v>
+        <v>32.27</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>49.17</v>
+        <v>45.26</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
@@ -1294,20 +1294,20 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>38.54</v>
+        <v>53.62</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>29.61</v>
+        <v>45.03</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>49.32</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>43.03</v>
+        <v>45.64</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>29.38</v>
+        <v>34.78</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>58.36</v>
+        <v>59.55</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>17.1</v>
+        <v>19.08</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>38.11</v>
+        <v>44.62</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>43.2</v>
+        <v>46.18</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>30.53</v>
+        <v>38.44</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.56</v>
+        <v>57.96</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
@@ -1490,20 +1490,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>39.88</v>
+        <v>45.43</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>31.7</v>
+        <v>37.75</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.54</v>
+        <v>62.04</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>24.95</v>
+        <v>23.06</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46.94</v>
+        <v>42.68</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>49.61</v>
+        <v>42.56</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>43.25</v>
+        <v>35.7</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>60.66</v>
+        <v>53.77</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>24.79</v>
+        <v>28.77</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>49.23</v>
+        <v>55.96</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>30.4</v>
+        <v>36.62</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>4.57</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>37.86</v>
+        <v>44.93</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
@@ -1650,20 +1650,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>48.35</v>
+        <v>39.7</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>38.34</v>
+        <v>29.75</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>67.72</v>
+        <v>56.7</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>22.72</v>
+        <v>28.41</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45.47</v>
+        <v>56.89</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46.48</v>
+        <v>41.57</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>35.11</v>
+        <v>32.28</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>60.99</v>
+        <v>56.32</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
@@ -1746,20 +1746,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>36.09</v>
+        <v>47.58</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>27.55</v>
+        <v>39.86</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>50.51</v>
+        <v>60.9</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1778,20 +1778,20 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>34.94</v>
+        <v>45.02</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.21</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>53.11</v>
+        <v>68.53</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1810,20 +1810,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>34.12</v>
+        <v>44.94</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>3.25</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>49.24</v>
+        <v>60.25</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46.63</v>
+        <v>44.81</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>35.12</v>
+        <v>35.93</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>58.81</v>
+        <v>58.16</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>43.41</v>
+        <v>47.86</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>35.31</v>
+        <v>40.97</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>58.63</v>
+        <v>60.46</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
@@ -1954,10 +1954,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39149</v>
+        <v>39424</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="3">
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>403123</v>
+        <v>310562</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>44.56</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>458449</v>
+        <v>553756</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>50.67</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>4034</v>
+        <v>1013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>904755</v>
+        <v>904753</v>
       </c>
     </row>
     <row r="7">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>68.53</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>40.36</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="10">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46.63</v>
+        <v>48.22</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>35.16</v>
+        <v>35.98</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>61.55</v>
+        <v>63.53</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44.07</v>
+        <v>45.9</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>30.99</v>
+        <v>31.59</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>58.79</v>
+        <v>60.77</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>37.84</v>
+        <v>37.85</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>42.28</v>
+        <v>44.15</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>36.29</v>
+        <v>37.15</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.98</v>
+        <v>57.63</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>42.43</v>
+        <v>44.39</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>35.43</v>
+        <v>37.41</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>50.83</v>
+        <v>52.81</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>54.24</v>
+        <v>56.14</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46.36</v>
+        <v>47.74</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>66.94</v>
+        <v>68.58</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>32.22</v>
+        <v>33.85</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>53.7</v>
+        <v>55.67</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45.39</v>
+        <v>45.42</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>35.27</v>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>41.88</v>
+        <v>43.38</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>32.44</v>
+        <v>33.04</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>53.46</v>
+        <v>55.43</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>42.09</v>
+        <v>43.3</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>33.05</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>59.65</v>
+        <v>61.29</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>42.47</v>
+        <v>44.37</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>33.16</v>
+        <v>34.59</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>57.52</v>
+        <v>59.17</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
@@ -1070,20 +1070,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>39.82</v>
+        <v>41.76</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>27.95</v>
+        <v>28.55</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>54.2</v>
+        <v>55.85</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>22.68</v>
+        <v>22.71</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>26.91</v>
+        <v>26.99</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45.34</v>
+        <v>46.98</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>36.51</v>
+        <v>37.33</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>62.66</v>
+        <v>64.63</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>27.1</v>
+        <v>27.12</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>49.6</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46.01</v>
+        <v>46.14</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>32.27</v>
+        <v>32.32</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>53.62</v>
+        <v>55.55</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>45.03</v>
+        <v>45.86</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>65.70999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45.64</v>
+        <v>47.37</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>34.78</v>
+        <v>35.37</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>59.55</v>
+        <v>61.3</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46.18</v>
+        <v>47.31</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>38.44</v>
+        <v>39.03</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>57.96</v>
+        <v>59.94</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45.43</v>
+        <v>47.3</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>37.75</v>
+        <v>38.68</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>62.04</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>23.06</v>
+        <v>23.08</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>42.56</v>
+        <v>44.25</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>35.7</v>
+        <v>36.53</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>53.77</v>
+        <v>55.74</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>28.77</v>
+        <v>30.38</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>55.96</v>
+        <v>57.94</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>36.62</v>
+        <v>38.59</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>4.57</v>
+        <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44.93</v>
+        <v>46.91</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
@@ -1650,20 +1650,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>39.7</v>
+        <v>41.02</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>29.75</v>
+        <v>30.35</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.7</v>
+        <v>58.67</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>41.57</v>
+        <v>42.9</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>32.28</v>
+        <v>32.88</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>56.32</v>
+        <v>57.97</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>47.58</v>
+        <v>49.41</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>39.86</v>
+        <v>40.57</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>60.9</v>
+        <v>62.87</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45.02</v>
+        <v>46.86</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>3.21</v>
+        <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>68.53</v>
+        <v>70.2</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44.94</v>
+        <v>46.72</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>3.25</v>
+        <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>60.25</v>
+        <v>62.22</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44.81</v>
+        <v>46.51</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>35.93</v>
+        <v>36.75</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>58.16</v>
+        <v>60.14</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>47.86</v>
+        <v>49.72</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>40.97</v>
+        <v>42.12</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>60.46</v>
+        <v>62.43</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
@@ -1954,7 +1954,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39424</v>
+        <v>39403</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>4.36</v>
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>310562</v>
+        <v>246062</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>34.33</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>553756</v>
+        <v>616574</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>61.21</v>
+        <v>68.15000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1013</v>
+        <v>2714</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -13,11 +13,7 @@
     <sheet name="طبقات_خطر" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="اطلاعات_فنی" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'مناطق_چهارگانه'!$A$1:$H$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'مناطق_شکار_ممنوع'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'طبقات_خطر'!$A$1:$E$6</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -25,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,18 +36,12 @@
     </font>
     <font>
       <name val="B Nazanin"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="B Nazanin"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,12 +54,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB8C00"/>
+        <fgColor rgb="008B0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B0000"/>
+        <fgColor rgb="00FB8C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,30 +109,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -510,132 +509,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>گزارش خطر حریق استان فارس</t>
+          <t>گزارش شاخص خطر حریق FIRIS</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>تاریخ پیش‌بینی</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>عنوان</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>مقدار</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>فایل FLI</t>
+          <t>عنوان</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-09-03.tif</t>
+          <t>شاخص خطر حریق FIRIS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>سیستم مختصات</t>
+          <t>تاریخ پیش‌بینی</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>EPSG:4326</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>تعداد سلول معتبر</t>
+          <t>حداقل FLI</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>904753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>حداقل FLI</t>
+          <t>حداکثر FLI</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0</v>
+        <v>70.19777679443359</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>حداکثر FLI</t>
+          <t>میانگین FLI</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>70.2</v>
+        <v>41.60722732543945</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>میانگین FLI</t>
+          <t>تعداد سلول‌های معتبر</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>41.61</v>
+        <v>904753</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>طبقه خطر استان</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+          <t>سیستم مختصات</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:4326</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>رزولوشن X</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>0.002588441050000003</v>
+          <t>ابعاد Raster</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2000 × 2000</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>رزولوشن Y</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>0.002411990949999999</v>
+          <t>تفکیک مکانی</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>0.002588441050000003 × 0.002411990949999999</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -648,184 +651,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>نوع منطقه</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>نام منطقه</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>نوع منطقه</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>میانگین FLI</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>حداقل FLI</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>حداکثر FLI</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>تعداد سلول معتبر</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>طبقه خطر</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوه خرسي</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>مناطق چهارگانه</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>48.22</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>35.98</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>63.53</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>24441</v>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع پادنا</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>مناطق چهارگانه</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>31.59</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>5703</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع دره باغ</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع کوه خرسي</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>37.85</v>
+        <v>35.98274230957031</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.43</v>
+        <v>63.52595520019531</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>56.89</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>751</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>48.21581649780273</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع کوه دراء</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع پادنا</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44.15</v>
+        <v>31.58595275878906</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>37.15</v>
+        <v>60.76916885375977</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>10563</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+        <v>45.9049072265625</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -833,63 +768,57 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع خرمنکوه</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع دره باغ</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44.39</v>
+        <v>0.4288939833641052</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>37.41</v>
+        <v>56.88711547851562</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>52.81</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1663</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>37.84542846679688</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع مل بلند</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع کوه دراء</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>56.14</v>
+        <v>37.15270614624023</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>47.74</v>
+        <v>57.62873840332031</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>68.58</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>2137</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+        <v>44.14516448974609</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -897,63 +826,57 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع دالان</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع خرمنکوه</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>33.85</v>
+        <v>37.40567398071289</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.01</v>
+        <v>52.81044387817383</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>44.39485168457031</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع توت سياه</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع مل بلند</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45.42</v>
+        <v>47.74176025390625</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>35.27</v>
+        <v>68.58392333984375</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>187</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
+        <v>56.14004898071289</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -961,63 +884,57 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع مهارلو</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع دالان</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>43.38</v>
+        <v>1.011088371276855</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>33.04</v>
+        <v>55.67188262939453</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>1059</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>33.84581756591797</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع روشن کوه</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع توت سياه</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>43.3</v>
+        <v>35.26800155639648</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>33.05</v>
+        <v>58.07172012329102</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>61.29</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>3976</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
+        <v>45.41751861572266</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1025,31 +942,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع کوه گورم</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع مهارلو</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44.37</v>
+        <v>33.04357147216797</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>34.59</v>
+        <v>55.43258285522461</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>5465</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+        <v>43.38051986694336</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1057,31 +971,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع کوهستان</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع روشن کوه</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>41.76</v>
+        <v>33.04644393920898</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>28.55</v>
+        <v>61.29364776611328</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>6849</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+        <v>43.29660415649414</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1089,127 +1000,115 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع چاه نفت</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع کوه گورم</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>22.71</v>
+        <v>34.5868034362793</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>1.06</v>
+        <v>59.16842651367188</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>31.86</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>44.3708610534668</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع مزايجان</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع کوهستان</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>26.99</v>
+        <v>28.55293083190918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.45</v>
+        <v>55.85193634033203</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>932</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>41.76459884643555</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع کوه سياه</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع چاه نفت</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46.98</v>
+        <v>1.059437394142151</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>37.33</v>
+        <v>31.8641242980957</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>64.63</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>4808</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>22.71386337280273</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع کوه هوا و</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع مزايجان</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>27.12</v>
+        <v>0.4496821761131287</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1.32</v>
+        <v>47.41470718383789</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>4944</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+        <v>26.98835945129395</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1217,31 +1116,28 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع بصيران</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع کوه سياه</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46.14</v>
+        <v>37.33026504516602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.65</v>
+        <v>64.63449859619141</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>5180</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
+        <v>46.98300933837891</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1249,31 +1145,28 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع بناب</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع کوه هوا و</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>32.32</v>
+        <v>1.317254424095154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>0.59</v>
+        <v>49.59907531738281</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45.26</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>3925</v>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+        <v>27.12177276611328</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1281,31 +1174,28 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممن.ع آق جلو</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع بصيران</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>55.55</v>
+        <v>0.6535705327987671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>45.86</v>
+        <v>62.79901123046875</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>67.69</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>657</v>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
+        <v>46.14044952392578</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1313,70 +1203,124 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>منطقه شکار ممنوع کوه خم</t>
+          <t>مناطق چهارگانه</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>مناطق چهارگانه</t>
+          <t>منطقه شکار ممنوع بناب</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>47.37</v>
+        <v>0.5927474498748779</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>35.37</v>
+        <v>45.25618743896484</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>6257</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>32.31592178344727</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممن.ع آق جلو</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45.85939788818359</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>67.68987274169922</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>55.54886627197266</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه خم</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>35.37437438964844</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>61.30070114135742</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>47.36817169189453</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>منطقه شکار ممنوع شیکوه</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>مناطق چهارگانه</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>19.08</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="D24" s="1" t="n">
+        <v>3.470377683639526</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>44.62166976928711</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>19.08002281188965</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>کم</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H22"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1388,184 +1332,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ردیف</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>نوع منطقه</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>نام منطقه</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>نوع منطقه</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>میانگین FLI</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>حداقل FLI</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>حداکثر FLI</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>تعداد سلول معتبر</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>طبقه خطر</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده تنگ بستانک</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>مناطق شکار ممنوع</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>47.31</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>59.94</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>2293</v>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده میانجنگل فسا</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>مناطق شکار ممنوع</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>38.68</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>4823</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>منطقه حفاظت شده هرمود</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>منطقه حفاظت شده تنگ بستانک</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>23.08</v>
+        <v>39.03468704223633</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.55</v>
+        <v>59.9395637512207</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>42.68</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>868</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>47.30693435668945</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>منطقه حفاظت شده مارگون</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>منطقه حفاظت شده میانجنگل فسا</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44.25</v>
+        <v>38.68421173095703</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>36.53</v>
+        <v>64.01129150390625</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.74</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>466</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+        <v>47.30406188964844</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1573,31 +1449,28 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>منطقه حفاظت شده بهرام گور</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>منطقه حفاظت شده هرمود</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>30.38</v>
+        <v>0.5461317896842957</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0</v>
+        <v>42.6773796081543</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>57.94</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>2048</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+        <v>23.07763481140137</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1605,95 +1478,86 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>پارک ملي قطرويه</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>منطقه حفاظت شده مارگون</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>38.59</v>
+        <v>36.52740859985352</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>6.54</v>
+        <v>55.74253082275391</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>173</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>44.25078964233398</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>منطقه حفاظت شده ارژن و پريشان</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>منطقه حفاظت شده بهرام گور</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>41.02</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>30.35</v>
+        <v>57.93932723999023</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>58.67</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>7042</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>30.3816032409668</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>پناهگاه حيات وحش دره باغ</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>پارک ملي قطرويه</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>28.41</v>
+        <v>6.544865608215332</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>9.050000000000001</v>
+        <v>46.90689849853516</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>56.89</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+        <v>38.59413528442383</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1701,31 +1565,28 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>منطقه حفاظت شده ماله گاله</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>منطقه حفاظت شده ارژن و پريشان</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>42.9</v>
+        <v>30.3493766784668</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>32.88</v>
+        <v>58.6745491027832</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>6931</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+        <v>41.0224723815918</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1733,63 +1594,57 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>پارک ملی بمو</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>پناهگاه حيات وحش دره باغ</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>49.41</v>
+        <v>9.053357124328613</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>40.57</v>
+        <v>56.88711547851562</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>62.87</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>5654</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>28.41498374938965</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>پناهگاه حيات وحش بختگان</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>منطقه حفاظت شده ماله گاله</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46.86</v>
+        <v>32.88029479980469</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>3.99</v>
+        <v>57.96788787841797</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>16529</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+        <v>42.89906692504883</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1797,31 +1652,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>پارک ملي بختگان</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>پارک ملی بمو</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46.72</v>
+        <v>40.56808853149414</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>4.03</v>
+        <v>62.87141418457031</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>62.22</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>5265</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
+        <v>49.40620422363281</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1829,31 +1681,28 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>منطقه حفاظت شده برم فیروز</t>
+          <t>مناطق شکار ممنوع</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>مناطق شکار ممنوع</t>
+          <t>پناهگاه حيات وحش بختگان</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46.51</v>
+        <v>3.987712860107422</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>36.75</v>
+        <v>70.19777679443359</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>60.14</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>2311</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
+        <v>46.86263656616211</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1861,38 +1710,95 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>پارک ملي بختگان</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>4.03125524520874</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>62.22476959228516</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>46.72356033325195</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده برم فیروز</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>36.74985122680664</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>60.13546752929688</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>46.5141487121582</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>مناطق شکار ممنوع</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>62.43</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>1185</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="D17" s="1" t="n">
+        <v>42.11957550048828</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>62.43229675292969</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>49.72004699707031</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1904,140 +1810,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>توزیع مکانی طبقات خطر FLI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>طبقه خطر</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>حداقل FLI</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>حداکثر FLI</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>تعداد سلول</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>درصد از کل</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>درصد از محدوده معتبر</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>کم</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D4" s="1" t="n">
         <v>39403</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="E4" s="7" t="n">
+        <v>4.355111284516327</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C5" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D5" s="1" t="n">
         <v>246062</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>27.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="E5" s="7" t="n">
+        <v>27.1965939875303</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C6" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>616574</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>68.15000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="n">
+        <v>68.14832335455091</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>خیلی زیاد</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B7" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C7" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>2714</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="E7" s="7" t="n">
+        <v>0.2999713734024645</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B8" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C8" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2049,166 +1965,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRS</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>EPSG:4326</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>2000</v>
-      </c>
-    </row>
+          <t>اطلاعات فنی و منابع داده</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>2000</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>پارامتر</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>مقدار</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>توضیح</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Resolution X</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>0.002588441050000003</v>
+          <t>تاریخ پیش‌بینی</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>تاریخ FLI مورد استفاده در گزارش</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Resolution Y</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>0.002411990949999999</v>
+          <t>Raster ورودی FLI</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>data/outputs/fli_fars_2026-09-03.tif</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Raster نهایی شاخص خطر حریق</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>50.5031831</v>
+          <t>مرجع مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>protected_areas.geojson</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>protected_areas.geojson</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Bottom</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>26.945617</v>
+          <t>مرجع مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>hunting_banned.geojson</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>hunting_banned.geojson</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>55.68006520000001</v>
+          <t>CRS</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:4326</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>سیستم مختصات Raster</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>عرض Raster</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>31.7695989</v>
+        <v>2000</v>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>تعداد ستون‌ها</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Transform a</t>
+          <t>ارتفاع Raster</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.002588441050000003</v>
+        <v>2000</v>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>تعداد ردیف‌ها</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Transform b</t>
+          <t>تفکیک X</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0</v>
+        <v>0.002588441050000003</v>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>تفکیک مکانی Raster</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Transform c</t>
+          <t>تفکیک Y</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>50.5031831</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Transform d</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Transform e</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>-0.002411990949999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Transform f</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>31.7695989</v>
+        <v>0.002411990949999999</v>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>تفکیک مکانی Raster</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,17 @@
     </font>
     <font>
       <name val="B Nazanin"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="B Nazanin"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -109,40 +120,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -586,7 +591,7 @@
           <t>میانگین FLI</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>41.60722732543945</v>
       </c>
     </row>
@@ -633,6 +638,18 @@
       <c r="B12" s="1" t="inlineStr">
         <is>
           <t>0.002588441050000003 × 0.002411990949999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>طبقه خطر استان</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -726,7 +743,7 @@
         <v>35.98274230957031</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>63.52595520019531</v>
+        <v>63.52596282958984</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>48.21581649780273</v>
@@ -789,7 +806,7 @@
       <c r="F6" s="1" t="n">
         <v>37.84542846679688</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -905,7 +922,7 @@
       <c r="F10" s="1" t="n">
         <v>33.84581756591797</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1079,7 +1096,7 @@
       <c r="F16" s="1" t="n">
         <v>22.71386337280273</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1108,7 +1125,7 @@
       <c r="F17" s="1" t="n">
         <v>26.98835945129395</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1166,7 +1183,7 @@
       <c r="F19" s="1" t="n">
         <v>27.12177276611328</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1190,7 +1207,7 @@
         <v>0.6535705327987671</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>62.79901123046875</v>
+        <v>62.79901885986328</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>46.14044952392578</v>
@@ -1224,7 +1241,7 @@
       <c r="F21" s="1" t="n">
         <v>32.31592178344727</v>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1311,7 +1328,7 @@
       <c r="F24" s="1" t="n">
         <v>19.08002281188965</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>کم</t>
         </is>
@@ -1470,7 +1487,7 @@
       <c r="F6" s="1" t="n">
         <v>23.07763481140137</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1528,7 +1545,7 @@
       <c r="F8" s="1" t="n">
         <v>30.3816032409668</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1557,7 +1574,7 @@
       <c r="F9" s="1" t="n">
         <v>38.59413528442383</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1615,7 +1632,7 @@
       <c r="F11" s="1" t="n">
         <v>28.41498374938965</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1814,9 +1831,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1875,7 +1892,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1894,7 +1911,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1913,7 +1930,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>خیلی زیاد</t>
         </is>
@@ -1932,7 +1949,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -13,7 +13,11 @@
     <sheet name="طبقات_خطر" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="اطلاعات_فنی" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'مناطق_چهارگانه'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'مناطق_شکار_ممنوع'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'طبقات_خطر'!$A$1:$E$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,17 +40,12 @@
     </font>
     <font>
       <name val="B Nazanin"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="B Nazanin"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -65,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B0000"/>
+        <fgColor rgb="00FB8C00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB8C00"/>
+        <fgColor rgb="008B0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,34 +119,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,148 +510,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>گزارش شاخص خطر حریق FIRIS</t>
+          <t>گزارش خطر حریق استان فارس</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>عنوان</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>مقدار</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>تاریخ پیش‌بینی</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>عنوان</t>
+          <t>فایل FLI</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>شاخص خطر حریق FIRIS</t>
+          <t>fli_fars_2026-09-03.tif</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>تاریخ پیش‌بینی</t>
+          <t>سیستم مختصات</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>EPSG:4326</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>حداقل FLI</t>
+          <t>تعداد سلول معتبر</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0</v>
+        <v>904753</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>حداکثر FLI</t>
+          <t>حداقل FLI</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>70.19777679443359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>میانگین FLI</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>41.60722732543945</v>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>70.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>تعداد سلول‌های معتبر</t>
+          <t>میانگین FLI</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>904753</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>سیستم مختصات</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>EPSG:4326</t>
+          <t>طبقه خطر استان</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ابعاد Raster</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>2000 × 2000</t>
-        </is>
+          <t>رزولوشن X</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.002588441050000003</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>تفکیک مکانی</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>0.002588441050000003 × 0.002411990949999999</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>طبقه خطر استان</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
+          <t>رزولوشن Y</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.002411990949999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -668,116 +648,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>نام منطقه</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>نوع منطقه</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>میانگین FLI</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>تعداد سلول معتبر</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>طبقه خطر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع کوه خرسي</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="D2" s="1" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>24441</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ردیف</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>نوع منطقه</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>نام منطقه</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>حداقل FLI</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>حداکثر FLI</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>میانگین FLI</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>طبقه خطر</t>
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>منطقه شکار ممنوع پادنا</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>مناطق چهارگانه</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>5703</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع دره باغ</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوه خرسي</t>
-        </is>
-      </c>
       <c r="D4" s="1" t="n">
-        <v>35.98274230957031</v>
+        <v>37.85</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>63.52596282958984</v>
+        <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>48.21581649780273</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>56.89</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>751</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع کوه دراء</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع پادنا</t>
-        </is>
-      </c>
       <c r="D5" s="1" t="n">
-        <v>31.58595275878906</v>
+        <v>44.15</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>60.76916885375977</v>
+        <v>37.15</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45.9049072265625</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+        <v>57.63</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>10563</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -785,57 +833,63 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع خرمنکوه</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع دره باغ</t>
-        </is>
-      </c>
       <c r="D6" s="1" t="n">
-        <v>0.4288939833641052</v>
+        <v>44.39</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>56.88711547851562</v>
+        <v>37.41</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>37.84542846679688</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>52.81</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1663</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع مل بلند</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوه دراء</t>
-        </is>
-      </c>
       <c r="D7" s="1" t="n">
-        <v>37.15270614624023</v>
+        <v>56.14</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>57.62873840332031</v>
+        <v>47.74</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44.14516448974609</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+        <v>68.58</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>2137</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -843,57 +897,63 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع دالان</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع خرمنکوه</t>
-        </is>
-      </c>
       <c r="D8" s="1" t="n">
-        <v>37.40567398071289</v>
+        <v>33.85</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>52.81044387817383</v>
+        <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>44.39485168457031</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>55.67</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع توت سياه</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع مل بلند</t>
-        </is>
-      </c>
       <c r="D9" s="1" t="n">
-        <v>47.74176025390625</v>
+        <v>45.42</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>68.58392333984375</v>
+        <v>35.27</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>56.14004898071289</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+        <v>58.07</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -901,57 +961,63 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع مهارلو</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع دالان</t>
-        </is>
-      </c>
       <c r="D10" s="1" t="n">
-        <v>1.011088371276855</v>
+        <v>43.38</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>55.67188262939453</v>
+        <v>33.04</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>33.84581756591797</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>55.43</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1059</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع روشن کوه</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع توت سياه</t>
-        </is>
-      </c>
       <c r="D11" s="1" t="n">
-        <v>35.26800155639648</v>
+        <v>43.3</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>58.07172012329102</v>
+        <v>33.05</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>45.41751861572266</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+        <v>61.29</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>3976</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -959,28 +1025,31 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع کوه گورم</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع مهارلو</t>
-        </is>
-      </c>
       <c r="D12" s="1" t="n">
-        <v>33.04357147216797</v>
+        <v>44.37</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>55.43258285522461</v>
+        <v>34.59</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>43.38051986694336</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+        <v>59.17</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>5465</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -988,28 +1057,31 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع کوهستان</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع روشن کوه</t>
-        </is>
-      </c>
       <c r="D13" s="1" t="n">
-        <v>33.04644393920898</v>
+        <v>41.76</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>61.29364776611328</v>
+        <v>28.55</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>43.29660415649414</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+        <v>55.85</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>6849</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1017,115 +1089,127 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع چاه نفت</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوه گورم</t>
-        </is>
-      </c>
       <c r="D14" s="1" t="n">
-        <v>34.5868034362793</v>
+        <v>22.71</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>59.16842651367188</v>
+        <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>44.3708610534668</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>31.86</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع مزايجان</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوهستان</t>
-        </is>
-      </c>
       <c r="D15" s="1" t="n">
-        <v>28.55293083190918</v>
+        <v>26.99</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>55.85193634033203</v>
+        <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>41.76459884643555</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>47.41</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>932</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع کوه سياه</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع چاه نفت</t>
-        </is>
-      </c>
       <c r="D16" s="1" t="n">
-        <v>1.059437394142151</v>
+        <v>46.98</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>31.8641242980957</v>
+        <v>37.33</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>22.71386337280273</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>64.63</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>4808</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع کوه هوا و</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع مزايجان</t>
-        </is>
-      </c>
       <c r="D17" s="1" t="n">
-        <v>0.4496821761131287</v>
+        <v>27.12</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>47.41470718383789</v>
+        <v>1.32</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>26.98835945129395</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+        <v>49.6</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>4944</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1133,28 +1217,31 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع بصيران</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوه سياه</t>
-        </is>
-      </c>
       <c r="D18" s="1" t="n">
-        <v>37.33026504516602</v>
+        <v>46.14</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>64.63449859619141</v>
+        <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46.98300933837891</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+        <v>62.8</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>5180</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1162,28 +1249,31 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع بناب</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوه هوا و</t>
-        </is>
-      </c>
       <c r="D19" s="1" t="n">
-        <v>1.317254424095154</v>
+        <v>32.32</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>49.59907531738281</v>
+        <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>27.12177276611328</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+        <v>45.26</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>3925</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1191,28 +1281,31 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممن.ع آق جلو</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع بصيران</t>
-        </is>
-      </c>
       <c r="D20" s="1" t="n">
-        <v>0.6535705327987671</v>
+        <v>55.55</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>62.79901885986328</v>
+        <v>45.86</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>46.14044952392578</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+        <v>67.69</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>657</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1220,124 +1313,70 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع کوه خم</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع بناب</t>
-        </is>
-      </c>
       <c r="D21" s="1" t="n">
-        <v>0.5927474498748779</v>
+        <v>47.37</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>45.25618743896484</v>
+        <v>35.37</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>32.31592178344727</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>61.3</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>6257</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
+          <t>منطقه شکار ممنوع شیکوه</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
           <t>مناطق چهارگانه</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممن.ع آق جلو</t>
-        </is>
-      </c>
       <c r="D22" s="1" t="n">
-        <v>45.85939788818359</v>
+        <v>19.08</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>67.68987274169922</v>
+        <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>55.54886627197266</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>مناطق چهارگانه</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع کوه خم</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>35.37437438964844</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>61.30070114135742</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>47.36817169189453</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>مناطق چهارگانه</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>منطقه شکار ممنوع شیکوه</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>3.470377683639526</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>44.62166976928711</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>19.08002281188965</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+        <v>44.62</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>کم</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <autoFilter ref="A1:H22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1349,116 +1388,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ردیف</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>نام منطقه</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>نوع منطقه</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>میانگین FLI</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>تعداد سلول معتبر</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>طبقه خطر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده تنگ بستانک</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="D2" s="1" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>59.94</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>2293</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ردیف</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>نوع منطقه</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>نام منطقه</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>حداقل FLI</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>حداکثر FLI</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>میانگین FLI</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>طبقه خطر</t>
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>منطقه حفاظت شده میانجنگل فسا</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>مناطق شکار ممنوع</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>4823</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
+          <t>منطقه حفاظت شده هرمود</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده تنگ بستانک</t>
-        </is>
-      </c>
       <c r="D4" s="1" t="n">
-        <v>39.03468704223633</v>
+        <v>23.08</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>59.9395637512207</v>
+        <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>47.30693435668945</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>42.68</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>868</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>منطقه حفاظت شده مارگون</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده میانجنگل فسا</t>
-        </is>
-      </c>
       <c r="D5" s="1" t="n">
-        <v>38.68421173095703</v>
+        <v>44.25</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>64.01129150390625</v>
+        <v>36.53</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>47.30406188964844</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+        <v>55.74</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>466</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1466,28 +1573,31 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
+          <t>منطقه حفاظت شده بهرام گور</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده هرمود</t>
-        </is>
-      </c>
       <c r="D6" s="1" t="n">
-        <v>0.5461317896842957</v>
+        <v>30.38</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>42.6773796081543</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>23.07763481140137</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+        <v>57.94</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1495,86 +1605,95 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
+          <t>پارک ملي قطرويه</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده مارگون</t>
-        </is>
-      </c>
       <c r="D7" s="1" t="n">
-        <v>36.52740859985352</v>
+        <v>38.59</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>55.74253082275391</v>
+        <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44.25078964233398</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+        <v>46.91</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
+          <t>منطقه حفاظت شده ارژن و پريشان</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده بهرام گور</t>
-        </is>
-      </c>
       <c r="D8" s="1" t="n">
-        <v>0</v>
+        <v>41.02</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>57.93932723999023</v>
+        <v>30.35</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>30.3816032409668</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>58.67</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>7042</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
+          <t>پناهگاه حيات وحش دره باغ</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>پارک ملي قطرويه</t>
-        </is>
-      </c>
       <c r="D9" s="1" t="n">
-        <v>6.544865608215332</v>
+        <v>28.41</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46.90689849853516</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>38.59413528442383</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+        <v>56.89</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1582,28 +1701,31 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>منطقه حفاظت شده ماله گاله</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده ارژن و پريشان</t>
-        </is>
-      </c>
       <c r="D10" s="1" t="n">
-        <v>30.3493766784668</v>
+        <v>42.9</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>58.6745491027832</v>
+        <v>32.88</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>41.0224723815918</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+        <v>57.97</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>6931</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1611,57 +1733,63 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
+          <t>پارک ملی بمو</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>پناهگاه حيات وحش دره باغ</t>
-        </is>
-      </c>
       <c r="D11" s="1" t="n">
-        <v>9.053357124328613</v>
+        <v>49.41</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>56.88711547851562</v>
+        <v>40.57</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>28.41498374938965</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+        <v>62.87</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>5654</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>پناهگاه حيات وحش بختگان</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده ماله گاله</t>
-        </is>
-      </c>
       <c r="D12" s="1" t="n">
-        <v>32.88029479980469</v>
+        <v>46.86</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>57.96788787841797</v>
+        <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>42.89906692504883</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+        <v>70.2</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>16529</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1669,28 +1797,31 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
+          <t>پارک ملي بختگان</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>پارک ملی بمو</t>
-        </is>
-      </c>
       <c r="D13" s="1" t="n">
-        <v>40.56808853149414</v>
+        <v>46.72</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>62.87141418457031</v>
+        <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>49.40620422363281</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+        <v>62.22</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>5265</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1698,28 +1829,31 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
+          <t>منطقه حفاظت شده برم فیروز</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>پناهگاه حيات وحش بختگان</t>
-        </is>
-      </c>
       <c r="D14" s="1" t="n">
-        <v>3.987712860107422</v>
+        <v>46.51</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>70.19777679443359</v>
+        <v>36.75</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46.86263656616211</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+        <v>60.14</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>2311</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1727,95 +1861,38 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
+          <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
           <t>مناطق شکار ممنوع</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>پارک ملي بختگان</t>
-        </is>
-      </c>
       <c r="D15" s="1" t="n">
-        <v>4.03125524520874</v>
+        <v>49.72</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>62.22476959228516</v>
+        <v>42.12</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46.72356033325195</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>مناطق شکار ممنوع</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده برم فیروز</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>36.74985122680664</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>60.13546752929688</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>46.5141487121582</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>مناطق شکار ممنوع</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>منطقه حفاظت شده تنگ سرخ و کوه قلات</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>42.11957550048828</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>62.43229675292969</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>49.72004699707031</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+        <v>62.43</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1185</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <autoFilter ref="A1:H15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1827,150 +1904,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>توزیع مکانی طبقات خطر FLI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>طبقه خطر</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>حداقل FLI</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>حداکثر FLI</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>تعداد سلول</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>درصد از کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>کم</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>39403</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>طبقه خطر</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>حداقل FLI</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>حداکثر FLI</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>تعداد سلول</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>درصد از محدوده معتبر</t>
-        </is>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>246062</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>27.2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>کم</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>616574</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>68.15000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>خیلی زیاد</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>2714</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>بحرانی</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>39403</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>4.355111284516327</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>246062</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>27.1965939875303</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>زیاد</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>616574</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>68.14832335455091</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>خیلی زیاد</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>2714</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>0.2999713734024645</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>بحرانی</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
+  <autoFilter ref="A1:E6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1982,188 +2049,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>اطلاعات فنی و منابع داده</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>CRS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:4326</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>2000</v>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>پارامتر</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>مقدار</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>توضیح</t>
-        </is>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>تاریخ پیش‌بینی</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>تاریخ FLI مورد استفاده در گزارش</t>
-        </is>
+          <t>Resolution X</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>0.002588441050000003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Raster ورودی FLI</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>data/outputs/fli_fars_2026-09-03.tif</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Raster نهایی شاخص خطر حریق</t>
-        </is>
+          <t>Resolution Y</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.002411990949999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>مرجع مناطق چهارگانه</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>protected_areas.geojson</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>protected_areas.geojson</t>
-        </is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>50.5031831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>مرجع مناطق شکار ممنوع</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>hunting_banned.geojson</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>hunting_banned.geojson</t>
-        </is>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>26.945617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CRS</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>EPSG:4326</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>سیستم مختصات Raster</t>
-        </is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>55.68006520000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>عرض Raster</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>تعداد ستون‌ها</t>
-        </is>
+        <v>31.7695989</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ارتفاع Raster</t>
+          <t>Transform a</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>تعداد ردیف‌ها</t>
-        </is>
+        <v>0.002588441050000003</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>تفکیک X</t>
+          <t>Transform b</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.002588441050000003</v>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>تفکیک مکانی Raster</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>تفکیک Y</t>
+          <t>Transform c</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.002411990949999999</v>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>تفکیک مکانی Raster</t>
-        </is>
+        <v>50.5031831</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Transform d</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Transform e</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>-0.002411990949999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Transform f</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>31.7695989</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB8C00"/>
+        <fgColor rgb="00FDD835"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDD835"/>
+        <fgColor rgb="00FB8C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,13 +127,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-09-03.tif</t>
+          <t>fli_fars_2026-09-04.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>70.2</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>41.61</v>
+        <v>37.63</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>48.22</v>
+        <v>42.11</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>35.98</v>
+        <v>26.66</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>63.53</v>
+        <v>60.44</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45.9</v>
+        <v>43.82</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>31.59</v>
+        <v>30.26</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>60.77</v>
+        <v>57.48</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>37.85</v>
+        <v>31.5</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>56.89</v>
+        <v>50.76</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44.15</v>
+        <v>44.49</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>37.15</v>
+        <v>36.83</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>57.63</v>
+        <v>58.44</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,20 +846,20 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44.39</v>
+        <v>39.63</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>37.41</v>
+        <v>31.35</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>52.81</v>
+        <v>48.87</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>56.14</v>
+        <v>42.57</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>47.74</v>
+        <v>31.71</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>68.58</v>
+        <v>55.07</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>33.85</v>
+        <v>36.96</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>55.67</v>
+        <v>55.82</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
@@ -942,20 +942,20 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45.42</v>
+        <v>36.37</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>35.27</v>
+        <v>29.28</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>58.07</v>
+        <v>50.1</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -974,20 +974,20 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>43.38</v>
+        <v>37.91</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>33.04</v>
+        <v>30.47</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>55.43</v>
+        <v>50.28</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>43.3</v>
+        <v>41.59</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>33.05</v>
+        <v>28.62</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>61.29</v>
+        <v>58.86</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44.37</v>
+        <v>42.77</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>34.59</v>
+        <v>28.46</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>59.17</v>
+        <v>58.81</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
@@ -1070,20 +1070,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>41.76</v>
+        <v>38.61</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>28.55</v>
+        <v>27.65</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>55.85</v>
+        <v>53.19</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>22.71</v>
+        <v>22.17</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>31.86</v>
+        <v>32.82</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>26.99</v>
+        <v>27.11</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>47.41</v>
+        <v>49.01</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46.98</v>
+        <v>42.71</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>37.33</v>
+        <v>30.04</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>64.63</v>
+        <v>57.58</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>27.12</v>
+        <v>27.18</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.32</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>49.6</v>
+        <v>48.27</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46.14</v>
+        <v>33.94</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>62.8</v>
+        <v>53.49</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>32.32</v>
+        <v>32.52</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45.26</v>
+        <v>47.03</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>55.55</v>
+        <v>40.55</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>45.86</v>
+        <v>29.84</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>67.69</v>
+        <v>51.32</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>47.37</v>
+        <v>43.48</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>35.37</v>
+        <v>32.16</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>61.3</v>
+        <v>58.11</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>19.08</v>
+        <v>18.37</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>44.62</v>
+        <v>42.08</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>47.31</v>
+        <v>42.25</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>39.03</v>
+        <v>33.23</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>59.94</v>
+        <v>54.88</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>47.3</v>
+        <v>42.45</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>38.68</v>
+        <v>33.04</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>64.01000000000001</v>
+        <v>62</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>23.08</v>
+        <v>23.52</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>42.68</v>
+        <v>44.07</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44.25</v>
+        <v>40.22</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>36.53</v>
+        <v>32.44</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.74</v>
+        <v>51.77</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>30.38</v>
+        <v>24.98</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>57.94</v>
+        <v>47.01</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>38.59</v>
+        <v>35.18</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46.91</v>
+        <v>43.22</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
@@ -1650,20 +1650,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>41.02</v>
+        <v>39.51</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>30.35</v>
+        <v>28.44</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>58.67</v>
+        <v>56.32</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>28.41</v>
+        <v>25.58</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>56.89</v>
+        <v>50.76</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>42.9</v>
+        <v>41.55</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>32.88</v>
+        <v>32.24</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>57.97</v>
+        <v>55.29</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>49.41</v>
+        <v>44.29</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>40.57</v>
+        <v>28.43</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>62.87</v>
+        <v>57.55</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
@@ -1778,20 +1778,20 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46.86</v>
+        <v>38.39</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>70.2</v>
+        <v>55.18</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1810,20 +1810,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46.72</v>
+        <v>37.18</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>62.22</v>
+        <v>54.15</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>زیاد</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46.51</v>
+        <v>43.8</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>36.75</v>
+        <v>33.88</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>60.14</v>
+        <v>57.25</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>49.72</v>
+        <v>46.8</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>42.12</v>
+        <v>38.52</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>62.43</v>
+        <v>59.96</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
@@ -1954,10 +1954,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39403</v>
+        <v>40236</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>4.36</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="3">
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>246062</v>
+        <v>476074</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>27.2</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>616574</v>
+        <v>388373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>68.15000000000001</v>
+        <v>42.93</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>2714</v>
+        <v>70</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>63.59</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>37.07</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="10">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>40.6</v>
+        <v>40.59</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>28.09</v>
+        <v>30.07</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.67</v>
+        <v>56.46</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>42.82</v>
+        <v>40.8</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>28.5</v>
+        <v>27.05</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.03</v>
+        <v>55.04</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>26.03</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>42.89</v>
+        <v>41.93</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>41.99</v>
+        <v>43.21</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>33.83</v>
+        <v>35.15</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.83</v>
+        <v>56.46</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>38.91</v>
+        <v>36.91</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>33</v>
+        <v>31.01</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>48.25</v>
+        <v>45.76</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>47.48</v>
+        <v>47.78</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>38.66</v>
+        <v>39.21</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>58.29</v>
+        <v>59.2</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>35.93</v>
+        <v>36.32</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>53.95</v>
+        <v>54.68</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>34.52</v>
+        <v>32.72</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>28.08</v>
+        <v>26.42</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>47.26</v>
+        <v>44.43</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>33.93</v>
+        <v>31.17</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>26.4</v>
+        <v>25.61</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45.42</v>
+        <v>41.3</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>39.36</v>
+        <v>39.89</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>28.45</v>
+        <v>27.59</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>54.72</v>
+        <v>56.21</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44.33</v>
+        <v>42.82</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>33.64</v>
+        <v>32.55</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>59.89</v>
+        <v>58.25</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>42.12</v>
+        <v>42.26</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>29.55</v>
+        <v>28.49</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>59.39</v>
+        <v>60.92</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>24.14</v>
+        <v>24.44</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>35.74</v>
+        <v>35.71</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>27.87</v>
+        <v>29.38</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46.59</v>
+        <v>49.18</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>41.68</v>
+        <v>40.76</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>29.62</v>
+        <v>31.15</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>56.66</v>
+        <v>55.92</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>26.19</v>
+        <v>27.09</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.32</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>47.13</v>
+        <v>48.7</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>34.19</v>
+        <v>33.13</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>52</v>
+        <v>48.85</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>34.33</v>
+        <v>32.33</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>49.26</v>
+        <v>46.73</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45.28</v>
+        <v>43.55</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>35.68</v>
+        <v>33.16</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>55.68</v>
+        <v>55.25</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>42.14</v>
+        <v>42.24</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>30.97</v>
+        <v>30.92</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>56.66</v>
+        <v>57.16</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>17.8</v>
+        <v>16.46</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>39.2</v>
+        <v>33.81</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39.49</v>
+        <v>38.69</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>30.88</v>
+        <v>28.6</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>52.35</v>
+        <v>51.57</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>41.52</v>
+        <v>40.47</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>33.08</v>
+        <v>30.6</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.1</v>
+        <v>58.75</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>23.63</v>
+        <v>23.9</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44.68</v>
+        <v>44.61</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
@@ -1554,20 +1554,20 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>39.44</v>
+        <v>40.57</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>32.8</v>
+        <v>34.08</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>50.25</v>
+        <v>51.53</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>25.73</v>
+        <v>24.17</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>50.74</v>
+        <v>46.19</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>31.92</v>
+        <v>30.22</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>39.35</v>
+        <v>37.7</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
@@ -1650,20 +1650,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>38.55</v>
+        <v>41.35</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>29.39</v>
+        <v>31.75</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>55.73</v>
+        <v>60.92</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>21.63</v>
+        <v>21.3</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>42.89</v>
+        <v>41.93</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
@@ -1714,20 +1714,20 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>39.59</v>
+        <v>41.06</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>30.19</v>
+        <v>30.15</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>53.27</v>
+        <v>58.02</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>42.3</v>
+        <v>41.13</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>31.22</v>
+        <v>31.5</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>56.08</v>
+        <v>55.01</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>36.38</v>
+        <v>36.28</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>54.38</v>
+        <v>52.74</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>34.87</v>
+        <v>35.26</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>51.46</v>
+        <v>50.55</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>41.15</v>
+        <v>41.34</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>32.43</v>
+        <v>32.6</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>54.17</v>
+        <v>55.09</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>42.8</v>
+        <v>42.09</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>34.55</v>
+        <v>33.67</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>55.97</v>
+        <v>55.32</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
@@ -1954,7 +1954,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39049</v>
+        <v>39048</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>4.32</v>
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>531588</v>
+        <v>526146</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>58.76</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>334088</v>
+        <v>339325</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>36.93</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDD835"/>
+        <fgColor rgb="00FB8C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB8C00"/>
+        <fgColor rgb="00FDD835"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,13 +127,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-09-06.tif</t>
+          <t>fli_fars_2026-09-07.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>62.4</v>
+        <v>68.93000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>37.63</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>41.27</v>
+        <v>46.42</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>28.31</v>
+        <v>35.63</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>57.97</v>
+        <v>62.85</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>41.93</v>
+        <v>45.23</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>27.13</v>
+        <v>30.29</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.73</v>
+        <v>61.56</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>25</v>
+        <v>28.26</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44.97</v>
+        <v>52.44</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>41.76</v>
+        <v>43.33</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>34.3</v>
+        <v>36.03</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>53.09</v>
+        <v>57.26</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,20 +846,20 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>37.52</v>
+        <v>42.73</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>29.05</v>
+        <v>33.86</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46.54</v>
+        <v>51.39</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45.53</v>
+        <v>51.86</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>36.7</v>
+        <v>42.21</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>58.27</v>
+        <v>63.4</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>32.41</v>
+        <v>39.06</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>50.05</v>
+        <v>56.81</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
@@ -942,20 +942,20 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>34.08</v>
+        <v>45.32</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>27.41</v>
+        <v>37.13</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45.43</v>
+        <v>58.46</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>33.21</v>
+        <v>37.83</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>27.09</v>
+        <v>30.42</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>42.24</v>
+        <v>49.13</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>40.71</v>
+        <v>45.04</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>28.41</v>
+        <v>34.25</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>57.27</v>
+        <v>61.41</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>43.25</v>
+        <v>43.57</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>32.11</v>
+        <v>32.21</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>59.44</v>
+        <v>59.49</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>41.97</v>
+        <v>42.48</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>28.95</v>
+        <v>28.9</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>61.18</v>
+        <v>61.48</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>25.65</v>
+        <v>26.35</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>38.85</v>
+        <v>38.94</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>31.26</v>
+        <v>31.32</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>51.73</v>
+        <v>53.42</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>42.2</v>
+        <v>43.18</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>31.54</v>
+        <v>33.48</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>57.07</v>
+        <v>58.56</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>28.17</v>
+        <v>33.02</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.32</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>49.24</v>
+        <v>57.05</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>34.89</v>
+        <v>40.42</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>54.18</v>
+        <v>57.1</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1262,20 +1262,20 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>38.5</v>
+        <v>43.17</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>54.28</v>
+        <v>61.26</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46.44</v>
+        <v>51.1</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>36.2</v>
+        <v>40.29</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>57.72</v>
+        <v>62.61</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>43.14</v>
+        <v>45.65</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>30.77</v>
+        <v>33.44</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>59.46</v>
+        <v>60.37</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
@@ -1358,20 +1358,20 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>16.64</v>
+        <v>20.33</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>35.14</v>
+        <v>50.38</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>کم</t>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>44.83</v>
+        <v>47.48</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>34.17</v>
+        <v>35.98</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>57.22</v>
+        <v>61.02</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
@@ -1490,20 +1490,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>38</v>
+        <v>43.38</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>30.18</v>
+        <v>32.17</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.3</v>
+        <v>59.42</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>24.23</v>
+        <v>24.74</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46.86</v>
+        <v>50.76</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>47.51</v>
+        <v>50.07</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>39.25</v>
+        <v>41.32</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>59.08</v>
+        <v>61.69</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>25.95</v>
+        <v>30.61</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>50.89</v>
+        <v>58.26</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,20 +1618,20 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>32.2</v>
+        <v>40.89</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>39.67</v>
+        <v>49.47</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1650,20 +1650,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>37.42</v>
+        <v>42.01</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>28.65</v>
+        <v>31.83</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>54.01</v>
+        <v>60.32</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>21.87</v>
+        <v>25.41</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>42.84</v>
+        <v>52.44</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>40.02</v>
+        <v>44.29</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>30.71</v>
+        <v>35.55</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>54.71</v>
+        <v>58.08</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>41.96</v>
+        <v>48.93</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>31.87</v>
+        <v>34.73</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>54.73</v>
+        <v>61.91</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
@@ -1778,20 +1778,20 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>37.59</v>
+        <v>45</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>58.07</v>
+        <v>62.77</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1810,20 +1810,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>37.35</v>
+        <v>44.42</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>52.81</v>
+        <v>62.55</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45.13</v>
+        <v>48.24</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>36.89</v>
+        <v>39.67</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>56.52</v>
+        <v>60.46</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>47.28</v>
+        <v>52.96</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>39.34</v>
+        <v>44.3</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>61.23</v>
+        <v>66.38</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>497375</v>
+        <v>255646</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>54.97</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>368310</v>
+        <v>608371</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>40.71</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>20</v>
+        <v>1688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB8C00"/>
+        <fgColor rgb="00FDD835"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDD835"/>
+        <fgColor rgb="00FB8C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,7 +127,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-09-07.tif</t>
+          <t>fli_fars_2026-09-08.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>68.93000000000001</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>41.51</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -718,20 +718,20 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46.42</v>
+        <v>39.71</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>35.63</v>
+        <v>26.99</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>62.85</v>
+        <v>56.82</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45.23</v>
+        <v>43.1</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>30.29</v>
+        <v>29.44</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>61.56</v>
+        <v>60.63</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -782,18 +782,18 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>28.26</v>
+        <v>27.84</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>52.44</v>
+        <v>48.06</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -814,18 +814,18 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>43.33</v>
+        <v>45.07</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>36.03</v>
+        <v>37.01</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>57.26</v>
+        <v>57.97</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -846,20 +846,20 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>42.73</v>
+        <v>36.53</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>33.86</v>
+        <v>28.73</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>51.39</v>
+        <v>45.62</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -878,18 +878,18 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>51.86</v>
+        <v>46.37</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>42.21</v>
+        <v>37.36</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>63.4</v>
+        <v>57.46</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>39.06</v>
+        <v>40.97</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.81</v>
+        <v>60.52</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -942,20 +942,20 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45.32</v>
+        <v>34.05</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>37.13</v>
+        <v>27.97</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>58.46</v>
+        <v>45.98</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -974,18 +974,18 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>37.83</v>
+        <v>34.01</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>30.42</v>
+        <v>26.49</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>49.13</v>
+        <v>45.39</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1006,20 +1006,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45.04</v>
+        <v>39.38</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>34.25</v>
+        <v>28.4</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>61.41</v>
+        <v>55.8</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1038,18 +1038,18 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>43.57</v>
+        <v>41.94</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>32.21</v>
+        <v>30.26</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>59.49</v>
+        <v>57.04</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1070,18 +1070,18 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>42.48</v>
+        <v>45.25</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>28.9</v>
+        <v>31.28</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>61.48</v>
+        <v>61.89</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1102,18 +1102,18 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>26.35</v>
+        <v>25.19</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>38.94</v>
+        <v>36.65</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1134,18 +1134,18 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>31.32</v>
+        <v>29.67</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>53.42</v>
+        <v>49.48</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1166,20 +1166,20 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>43.18</v>
+        <v>39.76</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>33.48</v>
+        <v>28.14</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>58.56</v>
+        <v>56.27</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>33.02</v>
+        <v>35.13</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.32</v>
@@ -1209,7 +1209,7 @@
       <c r="G17" s="1" t="n">
         <v>4944</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>40.42</v>
+        <v>33.59</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>57.1</v>
+        <v>49.33</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1262,18 +1262,18 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>43.17</v>
+        <v>43.83</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>61.26</v>
+        <v>62.1</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1294,18 +1294,18 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>51.1</v>
+        <v>40.02</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>40.29</v>
+        <v>30.28</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>62.61</v>
+        <v>51.74</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1326,18 +1326,18 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45.65</v>
+        <v>41.64</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>33.44</v>
+        <v>29.56</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>60.37</v>
+        <v>56.43</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1358,20 +1358,20 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>20.33</v>
+        <v>17.56</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>50.38</v>
+        <v>39.23</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>کم</t>
         </is>
       </c>
     </row>
@@ -1458,20 +1458,20 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>47.48</v>
+        <v>35.1</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>35.98</v>
+        <v>26.33</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>61.02</v>
+        <v>46.81</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1490,20 +1490,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>43.38</v>
+        <v>38.74</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>32.17</v>
+        <v>29.77</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>59.42</v>
+        <v>56.11</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1522,18 +1522,18 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>24.74</v>
+        <v>24.6</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>50.76</v>
+        <v>49.97</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1554,18 +1554,18 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>50.07</v>
+        <v>41.76</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>41.32</v>
+        <v>34.07</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>61.69</v>
+        <v>52.74</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1586,18 +1586,18 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>30.61</v>
+        <v>25.31</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>58.26</v>
+        <v>49.47</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1618,20 +1618,20 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>40.89</v>
+        <v>30.4</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>49.47</v>
+        <v>37.63</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1650,18 +1650,18 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>42.01</v>
+        <v>43.03</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>31.83</v>
+        <v>33.56</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>60.32</v>
+        <v>61.71</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1682,18 +1682,18 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>25.41</v>
+        <v>23.89</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>52.44</v>
+        <v>48.06</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1714,18 +1714,18 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44.29</v>
+        <v>41.54</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>35.55</v>
+        <v>32</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>58.08</v>
+        <v>56.21</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1746,20 +1746,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>48.93</v>
+        <v>37.34</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>34.73</v>
+        <v>28.42</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>61.91</v>
+        <v>50.35</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1778,20 +1778,20 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45</v>
+        <v>36.56</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>62.77</v>
+        <v>55.21</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1810,20 +1810,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44.42</v>
+        <v>36.38</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>62.55</v>
+        <v>52.1</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -1842,18 +1842,18 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>48.24</v>
+        <v>41.09</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>39.67</v>
+        <v>32.65</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>60.46</v>
+        <v>52.28</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1874,18 +1874,18 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>52.96</v>
+        <v>43.55</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>44.3</v>
+        <v>35.59</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>66.38</v>
+        <v>57.48</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1961,7 +1961,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1973,14 +1973,14 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>255646</v>
+        <v>448088</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>28.26</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>608371</v>
+        <v>415802</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>67.23999999999999</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1688</v>
+        <v>1815</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">

--- a/data/report/firis_report.xlsx
+++ b/data/report/firis_report.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="B Nazanin"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -64,7 +64,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDD835"/>
+        <fgColor rgb="00FB8C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +74,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FB8C00"/>
+        <fgColor rgb="00FDD835"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,7 +127,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,7 +533,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>fli_fars_2026-09-08.tif</t>
+          <t>fli_fars_2026-09-09.tif</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>70.19</v>
+        <v>68.43000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>38.18</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -718,20 +718,20 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39.71</v>
+        <v>45.25</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>26.99</v>
+        <v>34.11</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.82</v>
+        <v>64.86</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>43.1</v>
+        <v>43.62</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>29.44</v>
+        <v>30.93</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>60.63</v>
+        <v>57.38</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -782,18 +782,18 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>27.84</v>
+        <v>36.52</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>48.06</v>
+        <v>57.32</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -814,18 +814,18 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45.07</v>
+        <v>41.26</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>37.01</v>
+        <v>33.8</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>57.97</v>
+        <v>54.23</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -846,18 +846,18 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>36.53</v>
+        <v>39.15</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>28.73</v>
+        <v>31.67</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45.62</v>
+        <v>48.47</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -878,18 +878,18 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46.37</v>
+        <v>53.27</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>37.36</v>
+        <v>43.06</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>57.46</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>40.97</v>
+        <v>33.65</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>60.52</v>
+        <v>52.71</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>زیاد</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
@@ -942,20 +942,20 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>34.05</v>
+        <v>42.91</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>27.97</v>
+        <v>30.23</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45.98</v>
+        <v>55.23</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -974,18 +974,18 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>34.01</v>
+        <v>37.89</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>26.49</v>
+        <v>29.12</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45.39</v>
+        <v>52.66</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1006,20 +1006,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>39.38</v>
+        <v>41.69</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>55.8</v>
+        <v>59.66</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1038,18 +1038,18 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>41.94</v>
+        <v>42.45</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>30.26</v>
+        <v>32.14</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>57.04</v>
+        <v>60.02</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1070,18 +1070,18 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45.25</v>
+        <v>41.65</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>31.28</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>61.89</v>
+        <v>59.48</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1102,18 +1102,18 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>25.19</v>
+        <v>23.94</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>36.65</v>
+        <v>36.32</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1134,18 +1134,18 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>29.67</v>
+        <v>29.87</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>49.48</v>
+        <v>51</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1166,20 +1166,20 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>39.76</v>
+        <v>44.82</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>28.14</v>
+        <v>34.75</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>56.27</v>
+        <v>59.45</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1198,18 +1198,18 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>35.13</v>
+        <v>31.13</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.32</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>57.05</v>
+        <v>52.87</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>33.59</v>
+        <v>42.74</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>49.33</v>
+        <v>59.21</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1262,18 +1262,18 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>43.83</v>
+        <v>41.88</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>62.1</v>
+        <v>59.69</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1294,18 +1294,18 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>40.02</v>
+        <v>42.68</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>30.28</v>
+        <v>31.22</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>51.74</v>
+        <v>55.79</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1326,18 +1326,18 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>41.64</v>
+        <v>43.63</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>29.56</v>
+        <v>31.3</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>56.43</v>
+        <v>60.69</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>17.56</v>
+        <v>19.93</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>39.23</v>
+        <v>50.53</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,20 +1458,20 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>35.1</v>
+        <v>47.8</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>26.33</v>
+        <v>36.7</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46.81</v>
+        <v>61.38</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1490,20 +1490,20 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>38.74</v>
+        <v>44.66</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>29.77</v>
+        <v>35.09</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.11</v>
+        <v>61.48</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1522,18 +1522,18 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>24.6</v>
+        <v>24.95</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>49.97</v>
+        <v>49.88</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1554,18 +1554,18 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>41.76</v>
+        <v>52.36</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>34.07</v>
+        <v>44.47</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>52.74</v>
+        <v>63.78</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1586,18 +1586,18 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>25.31</v>
+        <v>26.79</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>49.47</v>
+        <v>53.75</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1618,18 +1618,18 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>30.4</v>
+        <v>32.6</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>37.63</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1650,18 +1650,18 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>43.03</v>
+        <v>40.32</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>33.56</v>
+        <v>29.3</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>61.71</v>
+        <v>58.61</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1682,18 +1682,18 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>23.89</v>
+        <v>28.65</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>48.06</v>
+        <v>57.32</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1714,18 +1714,18 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>41.54</v>
+        <v>42.79</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>32</v>
+        <v>33.21</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>56.21</v>
+        <v>56.86</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1746,20 +1746,20 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>37.34</v>
+        <v>42.97</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>28.42</v>
+        <v>30.19</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>50.35</v>
+        <v>59.64</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1778,20 +1778,20 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>36.56</v>
+        <v>41.38</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>55.21</v>
+        <v>61.72</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1810,20 +1810,20 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>36.38</v>
+        <v>40.63</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>52.1</v>
+        <v>55.82</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>متوسط</t>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1842,18 +1842,18 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>41.09</v>
+        <v>49.07</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>32.65</v>
+        <v>40.79</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>52.28</v>
+        <v>60.42</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1874,18 +1874,18 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>43.55</v>
+        <v>52.09</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>35.59</v>
+        <v>44.64</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>57.48</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1961,7 +1961,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
@@ -1973,14 +1973,14 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>448088</v>
+        <v>328992</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>49.53</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>زیاد</t>
         </is>
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>415802</v>
+        <v>535406</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45.96</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1815</v>
+        <v>1307</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="6">
